--- a/数据对比/cn指挥数据对比/世界赛.xlsx
+++ b/数据对比/cn指挥数据对比/世界赛.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\best igl wiki\数据对比\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\best igl wiki\数据对比\cn指挥数据对比\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5AA0C28-CEFA-45DA-B1EB-54FF401BB2E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E94D1DE6-772F-4CBF-BE0F-A72DBFD3359A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-31087" yWindow="-109" windowWidth="31196" windowHeight="18974" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -158,7 +158,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="13">
+  <numFmts count="14">
     <numFmt numFmtId="176" formatCode="[Color10]0;[Red]\-0;0"/>
     <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="178" formatCode="[Color10]0.00;[Red]\-0.00;0.00"/>
@@ -166,12 +166,13 @@
     <numFmt numFmtId="180" formatCode="0.0%"/>
     <numFmt numFmtId="181" formatCode="[Color10]0.0%;[Red]\-0.0%;0.0%"/>
     <numFmt numFmtId="182" formatCode="0.00_ "/>
-    <numFmt numFmtId="185" formatCode="[Color13][&gt;2.4]0.00;[Color3][&lt;1.2]0.00;[Color10]0.00"/>
-    <numFmt numFmtId="186" formatCode="[Color13][&gt;650]0.00;[Color3][&lt;350]0.00;[Color10]0.00"/>
-    <numFmt numFmtId="189" formatCode="[Color13][&gt;0.6]0.0%;[Color3][&lt;0.4]0.0%;[Color10]0.0%"/>
-    <numFmt numFmtId="190" formatCode="[Color13][&gt;0.16]0.0%;[Color3][&lt;0.24]0.0%;[Color10]0.0%"/>
-    <numFmt numFmtId="192" formatCode="[Color13][&lt;21]0;[Color3][&gt;30]0;[Color10]0"/>
-    <numFmt numFmtId="193" formatCode="[Color13][&gt;600]0.00;[Color3][&lt;350]0.00;[Color10]0.00"/>
+    <numFmt numFmtId="183" formatCode="[Color13][&gt;2.4]0.00;[Color3][&lt;1.2]0.00;[Color10]0.00"/>
+    <numFmt numFmtId="184" formatCode="[Color13][&gt;650]0.00;[Color3][&lt;350]0.00;[Color10]0.00"/>
+    <numFmt numFmtId="185" formatCode="[Color13][&gt;0.6]0.0%;[Color3][&lt;0.4]0.0%;[Color10]0.0%"/>
+    <numFmt numFmtId="186" formatCode="[Color13][&gt;0.16]0.0%;[Color3][&lt;0.24]0.0%;[Color10]0.0%"/>
+    <numFmt numFmtId="187" formatCode="[Color13][&lt;21]0;[Color3][&gt;30]0;[Color10]0"/>
+    <numFmt numFmtId="188" formatCode="[Color13][&gt;600]0.00;[Color3][&lt;350]0.00;[Color10]0.00"/>
+    <numFmt numFmtId="189" formatCode="[Color13][&gt;0.24]0.0%;[Color3][&lt;0.16]0.0%;[Color10]0.0%"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -209,7 +210,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -244,7 +245,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="183" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="185" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -253,16 +257,16 @@
     <xf numFmtId="186" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="189" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="187" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="190" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="188" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="192" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="193" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="189" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -555,11 +559,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
       <c r="D1" s="9" t="s">
         <v>0</v>
       </c>
@@ -615,15 +619,15 @@
       <c r="AB1" s="1"/>
     </row>
     <row r="2" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
       <c r="D2" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="17">
+      <c r="E2" s="16">
         <v>25</v>
       </c>
       <c r="F2" s="10">
@@ -638,7 +642,7 @@
       <c r="I2" s="10">
         <v>35</v>
       </c>
-      <c r="J2" s="13">
+      <c r="J2" s="12">
         <f>(G2+H2)/I2</f>
         <v>1.0857142857142856</v>
       </c>
@@ -651,17 +655,17 @@
       <c r="M2" s="10">
         <v>-3616</v>
       </c>
-      <c r="N2" s="18">
+      <c r="N2" s="17">
         <f>K2/F2</f>
         <v>530.56666666666672</v>
       </c>
-      <c r="O2" s="15">
+      <c r="O2" s="14">
         <v>0.433</v>
       </c>
-      <c r="P2" s="15">
+      <c r="P2" s="14">
         <v>0.38500000000000001</v>
       </c>
-      <c r="Q2" s="16">
+      <c r="Q2" s="19">
         <v>0</v>
       </c>
       <c r="R2" s="1"/>
@@ -677,13 +681,13 @@
       <c r="AB2" s="1"/>
     </row>
     <row r="3" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="12"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
+      <c r="A3" s="18"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
       <c r="D3" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="17">
+      <c r="E3" s="16">
         <v>23</v>
       </c>
       <c r="F3" s="9">
@@ -698,7 +702,7 @@
       <c r="I3" s="9">
         <v>31</v>
       </c>
-      <c r="J3" s="13">
+      <c r="J3" s="12">
         <f>(G3+H3)/I3</f>
         <v>1.064516129032258</v>
       </c>
@@ -711,17 +715,17 @@
       <c r="M3" s="9">
         <v>-1197</v>
       </c>
-      <c r="N3" s="18">
+      <c r="N3" s="17">
         <f>K3/F3</f>
         <v>488.93333333333334</v>
       </c>
-      <c r="O3" s="15">
+      <c r="O3" s="14">
         <v>0.5</v>
       </c>
-      <c r="P3" s="15">
+      <c r="P3" s="14">
         <v>0.66700000000000004</v>
       </c>
-      <c r="Q3" s="16">
+      <c r="Q3" s="19">
         <v>0.1</v>
       </c>
       <c r="R3" s="1"/>
@@ -737,13 +741,13 @@
       <c r="AB3" s="1"/>
     </row>
     <row r="4" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
       <c r="D4" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" s="16" t="s">
         <v>28</v>
       </c>
       <c r="F4" s="11" t="s">
@@ -758,7 +762,7 @@
       <c r="I4" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="J4" s="13" t="s">
+      <c r="J4" s="12" t="s">
         <v>28</v>
       </c>
       <c r="K4" s="11" t="s">
@@ -770,16 +774,16 @@
       <c r="M4" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="O4" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="P4" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q4" s="16" t="s">
+      <c r="N4" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="O4" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="P4" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q4" s="19" t="s">
         <v>28</v>
       </c>
       <c r="R4" s="1"/>
@@ -795,13 +799,13 @@
       <c r="AB4" s="1"/>
     </row>
     <row r="5" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="12"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
+      <c r="A5" s="18"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
       <c r="D5" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="16">
         <v>40</v>
       </c>
       <c r="F5" s="11">
@@ -816,7 +820,7 @@
       <c r="I5" s="11">
         <v>24</v>
       </c>
-      <c r="J5" s="13">
+      <c r="J5" s="12">
         <f>(G5+H5)/I5</f>
         <v>0.58333333333333337</v>
       </c>
@@ -827,20 +831,20 @@
         <v>17451</v>
       </c>
       <c r="M5" s="11">
-        <f t="shared" ref="M5:M7" si="0">K5-L5</f>
+        <f t="shared" ref="M5" si="0">K5-L5</f>
         <v>-4657</v>
       </c>
-      <c r="N5" s="18">
+      <c r="N5" s="17">
         <f>K5/F5</f>
         <v>533.08333333333337</v>
       </c>
-      <c r="O5" s="15">
+      <c r="O5" s="14">
         <v>0.25</v>
       </c>
-      <c r="P5" s="15">
+      <c r="P5" s="14">
         <v>0.66700000000000004</v>
       </c>
-      <c r="Q5" s="16">
+      <c r="Q5" s="19">
         <v>0</v>
       </c>
       <c r="R5" s="11"/>
@@ -856,13 +860,13 @@
       <c r="AB5" s="11"/>
     </row>
     <row r="6" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="12"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
       <c r="D6" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="16" t="s">
         <v>28</v>
       </c>
       <c r="F6" s="11" t="s">
@@ -877,7 +881,7 @@
       <c r="I6" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="J6" s="13" t="s">
+      <c r="J6" s="12" t="s">
         <v>28</v>
       </c>
       <c r="K6" s="11" t="s">
@@ -889,16 +893,16 @@
       <c r="M6" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="N6" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="O6" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="P6" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q6" s="16" t="s">
+      <c r="N6" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="O6" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="P6" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q6" s="19" t="s">
         <v>28</v>
       </c>
       <c r="R6" s="11"/>
@@ -914,13 +918,13 @@
       <c r="AB6" s="11"/>
     </row>
     <row r="7" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="12"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
+      <c r="A7" s="18"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
       <c r="D7" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="16" t="s">
         <v>28</v>
       </c>
       <c r="F7" s="11" t="s">
@@ -935,7 +939,7 @@
       <c r="I7" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="J7" s="13" t="s">
+      <c r="J7" s="12" t="s">
         <v>28</v>
       </c>
       <c r="K7" s="11" t="s">
@@ -947,16 +951,16 @@
       <c r="M7" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="N7" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="O7" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="P7" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q7" s="16" t="s">
+      <c r="N7" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="O7" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="P7" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q7" s="19" t="s">
         <v>28</v>
       </c>
       <c r="R7" s="11"/>
@@ -972,11 +976,11 @@
       <c r="AB7" s="11"/>
     </row>
     <row r="8" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
       <c r="D8" s="11" t="s">
         <v>0</v>
       </c>
@@ -1032,15 +1036,15 @@
       <c r="AB8" s="11"/>
     </row>
     <row r="9" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
       <c r="D9" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="16">
         <v>1</v>
       </c>
       <c r="F9" s="11">
@@ -1055,7 +1059,7 @@
       <c r="I9" s="11">
         <v>16</v>
       </c>
-      <c r="J9" s="13">
+      <c r="J9" s="12">
         <f>(G9+H9)/I9</f>
         <v>3.125</v>
       </c>
@@ -1068,17 +1072,17 @@
       <c r="M9" s="11">
         <v>-88</v>
       </c>
-      <c r="N9" s="18">
+      <c r="N9" s="17">
         <f>K9/F9</f>
         <v>731.36842105263156</v>
       </c>
-      <c r="O9" s="15">
+      <c r="O9" s="14">
         <v>0.73699999999999999</v>
       </c>
-      <c r="P9" s="15">
+      <c r="P9" s="14">
         <v>0.64300000000000002</v>
       </c>
-      <c r="Q9" s="16">
+      <c r="Q9" s="19">
         <v>0.33300000000000002</v>
       </c>
       <c r="R9" s="11"/>
@@ -1094,13 +1098,13 @@
       <c r="AB9" s="11"/>
     </row>
     <row r="10" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="12"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
       <c r="D10" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="16">
         <v>5</v>
       </c>
       <c r="F10" s="11">
@@ -1115,7 +1119,7 @@
       <c r="I10" s="11">
         <v>18</v>
       </c>
-      <c r="J10" s="13">
+      <c r="J10" s="12">
         <f>(G10+H10)/I10</f>
         <v>1.8888888888888888</v>
       </c>
@@ -1128,17 +1132,17 @@
       <c r="M10" s="11">
         <v>-3352</v>
       </c>
-      <c r="N10" s="18">
+      <c r="N10" s="17">
         <f>K10/F10</f>
         <v>423.26315789473682</v>
       </c>
-      <c r="O10" s="15">
+      <c r="O10" s="14">
         <v>0.63200000000000001</v>
       </c>
-      <c r="P10" s="15">
+      <c r="P10" s="14">
         <v>0.83299999999999996</v>
       </c>
-      <c r="Q10" s="16">
+      <c r="Q10" s="19">
         <v>0.1</v>
       </c>
       <c r="R10" s="11"/>
@@ -1154,13 +1158,13 @@
       <c r="AB10" s="11"/>
     </row>
     <row r="11" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="12"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
       <c r="D11" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="16">
         <v>37</v>
       </c>
       <c r="F11" s="11">
@@ -1175,7 +1179,7 @@
       <c r="I11" s="11">
         <v>10</v>
       </c>
-      <c r="J11" s="13">
+      <c r="J11" s="12">
         <f>(G11+H11)/I11</f>
         <v>1.1000000000000001</v>
       </c>
@@ -1188,17 +1192,17 @@
       <c r="M11" s="11">
         <v>-1033</v>
       </c>
-      <c r="N11" s="18">
+      <c r="N11" s="17">
         <f>K11/F11</f>
         <v>271.39999999999998</v>
       </c>
-      <c r="O11" s="15">
+      <c r="O11" s="14">
         <v>0.3</v>
       </c>
-      <c r="P11" s="15">
+      <c r="P11" s="14">
         <v>1</v>
       </c>
-      <c r="Q11" s="16">
+      <c r="Q11" s="19">
         <v>0</v>
       </c>
       <c r="R11" s="11"/>
@@ -1214,13 +1218,13 @@
       <c r="AB11" s="11"/>
     </row>
     <row r="12" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
       <c r="D12" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="16">
         <v>30</v>
       </c>
       <c r="F12" s="11">
@@ -1235,7 +1239,7 @@
       <c r="I12" s="11">
         <v>23</v>
       </c>
-      <c r="J12" s="13">
+      <c r="J12" s="12">
         <f>(G12+H12)/I12</f>
         <v>1.3913043478260869</v>
       </c>
@@ -1246,20 +1250,20 @@
         <v>13224</v>
       </c>
       <c r="M12" s="11">
-        <f t="shared" ref="M12:M14" si="1">K12-L12</f>
+        <f t="shared" ref="M12" si="1">K12-L12</f>
         <v>-948</v>
       </c>
-      <c r="N12" s="18">
+      <c r="N12" s="17">
         <f>K12/F12</f>
         <v>613.79999999999995</v>
       </c>
-      <c r="O12" s="15">
+      <c r="O12" s="14">
         <v>0.45</v>
       </c>
-      <c r="P12" s="15">
+      <c r="P12" s="14">
         <v>0.33300000000000002</v>
       </c>
-      <c r="Q12" s="16">
+      <c r="Q12" s="19">
         <v>0</v>
       </c>
       <c r="R12" s="11"/>
@@ -1275,13 +1279,13 @@
       <c r="AB12" s="11"/>
     </row>
     <row r="13" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="12"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
+      <c r="A13" s="18"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
       <c r="D13" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="E13" s="17" t="s">
+      <c r="E13" s="16" t="s">
         <v>28</v>
       </c>
       <c r="F13" s="11" t="s">
@@ -1296,7 +1300,7 @@
       <c r="I13" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="J13" s="13" t="s">
+      <c r="J13" s="12" t="s">
         <v>28</v>
       </c>
       <c r="K13" s="11" t="s">
@@ -1308,16 +1312,16 @@
       <c r="M13" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="N13" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="O13" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="P13" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q13" s="16" t="s">
+      <c r="N13" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="O13" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="P13" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q13" s="19" t="s">
         <v>28</v>
       </c>
       <c r="R13" s="11"/>
@@ -1333,13 +1337,13 @@
       <c r="AB13" s="11"/>
     </row>
     <row r="14" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="12"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
       <c r="D14" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="E14" s="16" t="s">
         <v>28</v>
       </c>
       <c r="F14" s="11" t="s">
@@ -1354,7 +1358,7 @@
       <c r="I14" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="J14" s="13" t="s">
+      <c r="J14" s="12" t="s">
         <v>28</v>
       </c>
       <c r="K14" s="11" t="s">
@@ -1366,16 +1370,16 @@
       <c r="M14" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="N14" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="O14" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="P14" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q14" s="16" t="s">
+      <c r="N14" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="O14" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="P14" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q14" s="19" t="s">
         <v>28</v>
       </c>
       <c r="R14" s="11"/>
@@ -1391,11 +1395,11 @@
       <c r="AB14" s="11"/>
     </row>
     <row r="15" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
       <c r="D15" s="11" t="s">
         <v>0</v>
       </c>
@@ -1451,15 +1455,15 @@
       <c r="AB15" s="11"/>
     </row>
     <row r="16" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
       <c r="D16" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="E16" s="17">
+      <c r="E16" s="16">
         <v>17</v>
       </c>
       <c r="F16" s="11">
@@ -1474,7 +1478,7 @@
       <c r="I16" s="11">
         <v>45</v>
       </c>
-      <c r="J16" s="13">
+      <c r="J16" s="12">
         <f>(G16+H16)/I16</f>
         <v>1.5111111111111111</v>
       </c>
@@ -1487,17 +1491,17 @@
       <c r="M16" s="11">
         <v>-6267</v>
       </c>
-      <c r="N16" s="18">
+      <c r="N16" s="17">
         <f>K16/F16</f>
         <v>607.63888888888891</v>
       </c>
-      <c r="O16" s="15">
+      <c r="O16" s="14">
         <v>0.63900000000000001</v>
       </c>
-      <c r="P16" s="15">
+      <c r="P16" s="14">
         <v>0.65200000000000002</v>
       </c>
-      <c r="Q16" s="16">
+      <c r="Q16" s="19">
         <v>0.13300000000000001</v>
       </c>
       <c r="R16" s="11"/>
@@ -1513,13 +1517,13 @@
       <c r="AB16" s="11"/>
     </row>
     <row r="17" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="12"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
+      <c r="A17" s="18"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
       <c r="D17" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E17" s="17" t="s">
+      <c r="E17" s="16" t="s">
         <v>28</v>
       </c>
       <c r="F17" s="11" t="s">
@@ -1534,7 +1538,7 @@
       <c r="I17" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="J17" s="13" t="s">
+      <c r="J17" s="12" t="s">
         <v>28</v>
       </c>
       <c r="K17" s="11" t="s">
@@ -1546,16 +1550,16 @@
       <c r="M17" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="N17" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="O17" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="P17" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q17" s="16" t="s">
+      <c r="N17" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="O17" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="P17" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q17" s="19" t="s">
         <v>28</v>
       </c>
       <c r="R17" s="11"/>
@@ -1571,13 +1575,13 @@
       <c r="AB17" s="11"/>
     </row>
     <row r="18" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="12"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
       <c r="D18" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E18" s="17" t="s">
+      <c r="E18" s="16" t="s">
         <v>28</v>
       </c>
       <c r="F18" s="11" t="s">
@@ -1592,7 +1596,7 @@
       <c r="I18" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="J18" s="13" t="s">
+      <c r="J18" s="12" t="s">
         <v>28</v>
       </c>
       <c r="K18" s="11" t="s">
@@ -1604,16 +1608,16 @@
       <c r="M18" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="N18" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="O18" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="P18" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q18" s="16" t="s">
+      <c r="N18" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="O18" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="P18" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q18" s="19" t="s">
         <v>28</v>
       </c>
       <c r="R18" s="11"/>
@@ -1629,13 +1633,13 @@
       <c r="AB18" s="11"/>
     </row>
     <row r="19" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
+      <c r="A19" s="18"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
       <c r="D19" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="17">
+      <c r="E19" s="16">
         <v>56</v>
       </c>
       <c r="F19" s="11">
@@ -1650,7 +1654,7 @@
       <c r="I19" s="11">
         <v>29</v>
       </c>
-      <c r="J19" s="13">
+      <c r="J19" s="12">
         <f>(G19+H19)/I19</f>
         <v>2.9655172413793105</v>
       </c>
@@ -1661,20 +1665,20 @@
         <v>13600</v>
       </c>
       <c r="M19" s="11">
-        <f t="shared" ref="M19:M21" si="2">K19-L19</f>
+        <f t="shared" ref="M19" si="2">K19-L19</f>
         <v>1490</v>
       </c>
-      <c r="N19" s="18">
+      <c r="N19" s="17">
         <f>K19/F19</f>
         <v>503</v>
       </c>
-      <c r="O19" s="15">
+      <c r="O19" s="14">
         <v>0.56699999999999995</v>
       </c>
-      <c r="P19" s="15">
+      <c r="P19" s="14">
         <v>0.52900000000000003</v>
       </c>
-      <c r="Q19" s="16">
+      <c r="Q19" s="19">
         <v>0.33300000000000002</v>
       </c>
       <c r="R19" s="11"/>
@@ -1690,13 +1694,13 @@
       <c r="AB19" s="11"/>
     </row>
     <row r="20" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="12"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
+      <c r="A20" s="18"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
       <c r="D20" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="E20" s="17" t="s">
+      <c r="E20" s="16" t="s">
         <v>28</v>
       </c>
       <c r="F20" s="11" t="s">
@@ -1711,7 +1715,7 @@
       <c r="I20" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="J20" s="13" t="s">
+      <c r="J20" s="12" t="s">
         <v>28</v>
       </c>
       <c r="K20" s="11" t="s">
@@ -1723,16 +1727,16 @@
       <c r="M20" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="N20" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="O20" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="P20" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q20" s="16" t="s">
+      <c r="N20" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="O20" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="P20" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q20" s="19" t="s">
         <v>28</v>
       </c>
       <c r="R20" s="11"/>
@@ -1748,13 +1752,13 @@
       <c r="AB20" s="11"/>
     </row>
     <row r="21" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="12"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
+      <c r="A21" s="18"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="18"/>
       <c r="D21" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="E21" s="17" t="s">
+      <c r="E21" s="16" t="s">
         <v>28</v>
       </c>
       <c r="F21" s="11" t="s">
@@ -1769,7 +1773,7 @@
       <c r="I21" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="J21" s="13" t="s">
+      <c r="J21" s="12" t="s">
         <v>28</v>
       </c>
       <c r="K21" s="11" t="s">
@@ -1781,16 +1785,16 @@
       <c r="M21" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="N21" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="O21" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="P21" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q21" s="16" t="s">
+      <c r="N21" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="O21" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="P21" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q21" s="19" t="s">
         <v>28</v>
       </c>
       <c r="R21" s="11"/>
@@ -1806,11 +1810,11 @@
       <c r="AB21" s="11"/>
     </row>
     <row r="22" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
       <c r="D22" s="11" t="s">
         <v>0</v>
       </c>
@@ -1866,15 +1870,15 @@
       <c r="AB22" s="11"/>
     </row>
     <row r="23" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="12" t="s">
+      <c r="A23" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="18"/>
       <c r="D23" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="E23" s="17">
+      <c r="E23" s="16">
         <v>9</v>
       </c>
       <c r="F23" s="11">
@@ -1889,7 +1893,7 @@
       <c r="I23" s="11">
         <v>51</v>
       </c>
-      <c r="J23" s="13">
+      <c r="J23" s="12">
         <f>(G23+H23)/I23</f>
         <v>1.8235294117647058</v>
       </c>
@@ -1902,17 +1906,17 @@
       <c r="M23" s="11">
         <v>-6739</v>
       </c>
-      <c r="N23" s="18">
+      <c r="N23" s="17">
         <f>K23/F23</f>
         <v>692.67441860465112</v>
       </c>
-      <c r="O23" s="15">
+      <c r="O23" s="14">
         <v>0.65100000000000002</v>
       </c>
-      <c r="P23" s="15">
+      <c r="P23" s="14">
         <v>0.57099999999999995</v>
       </c>
-      <c r="Q23" s="16">
+      <c r="Q23" s="19">
         <v>6.3E-2</v>
       </c>
       <c r="R23" s="11"/>
@@ -1928,13 +1932,13 @@
       <c r="AB23" s="11"/>
     </row>
     <row r="24" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="12"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
+      <c r="A24" s="18"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
       <c r="D24" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E24" s="17" t="s">
+      <c r="E24" s="16" t="s">
         <v>28</v>
       </c>
       <c r="F24" s="11" t="s">
@@ -1949,7 +1953,7 @@
       <c r="I24" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="J24" s="13" t="s">
+      <c r="J24" s="12" t="s">
         <v>28</v>
       </c>
       <c r="K24" s="11" t="s">
@@ -1961,16 +1965,16 @@
       <c r="M24" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="N24" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="O24" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="P24" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q24" s="16" t="s">
+      <c r="N24" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="O24" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="P24" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q24" s="19" t="s">
         <v>28</v>
       </c>
       <c r="R24" s="11"/>
@@ -1986,13 +1990,13 @@
       <c r="AB24" s="11"/>
     </row>
     <row r="25" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="12"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
+      <c r="A25" s="18"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="18"/>
       <c r="D25" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E25" s="17">
+      <c r="E25" s="16">
         <v>35</v>
       </c>
       <c r="F25" s="11">
@@ -2007,7 +2011,7 @@
       <c r="I25" s="11">
         <v>26</v>
       </c>
-      <c r="J25" s="13">
+      <c r="J25" s="12">
         <f>(G25+H25)/I25</f>
         <v>1.5384615384615385</v>
       </c>
@@ -2020,17 +2024,17 @@
       <c r="M25" s="11">
         <v>-4727</v>
       </c>
-      <c r="N25" s="18">
+      <c r="N25" s="17">
         <f>K25/F25</f>
         <v>473.30769230769232</v>
       </c>
-      <c r="O25" s="15">
+      <c r="O25" s="14">
         <v>0.46200000000000002</v>
       </c>
-      <c r="P25" s="15">
+      <c r="P25" s="14">
         <v>0.33300000000000002</v>
       </c>
-      <c r="Q25" s="16">
+      <c r="Q25" s="19">
         <v>0</v>
       </c>
       <c r="R25" s="11"/>
@@ -2046,13 +2050,13 @@
       <c r="AB25" s="11"/>
     </row>
     <row r="26" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="12"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
+      <c r="A26" s="18"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="18"/>
       <c r="D26" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="E26" s="17">
+      <c r="E26" s="16">
         <v>33</v>
       </c>
       <c r="F26" s="11">
@@ -2067,7 +2071,7 @@
       <c r="I26" s="11">
         <v>29</v>
       </c>
-      <c r="J26" s="13">
+      <c r="J26" s="12">
         <f>(G26+H26)/I26</f>
         <v>1.5517241379310345</v>
       </c>
@@ -2078,20 +2082,20 @@
         <v>20834</v>
       </c>
       <c r="M26" s="11">
-        <f t="shared" ref="M26:M28" si="3">K26-L26</f>
+        <f t="shared" ref="M26" si="3">K26-L26</f>
         <v>-4152</v>
       </c>
-      <c r="N26" s="18">
+      <c r="N26" s="17">
         <f>K26/F26</f>
         <v>641.61538461538464</v>
       </c>
-      <c r="O26" s="15">
+      <c r="O26" s="14">
         <v>0.46200000000000002</v>
       </c>
-      <c r="P26" s="15">
+      <c r="P26" s="14">
         <v>0.58299999999999996</v>
       </c>
-      <c r="Q26" s="16">
+      <c r="Q26" s="19">
         <v>0</v>
       </c>
       <c r="R26" s="11"/>
@@ -2107,13 +2111,13 @@
       <c r="AB26" s="11"/>
     </row>
     <row r="27" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="12"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
+      <c r="A27" s="18"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="18"/>
       <c r="D27" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="E27" s="17">
+      <c r="E27" s="16">
         <v>38</v>
       </c>
       <c r="F27" s="11">
@@ -2128,7 +2132,7 @@
       <c r="I27" s="11">
         <v>26</v>
       </c>
-      <c r="J27" s="13">
+      <c r="J27" s="12">
         <f>(G27+H27)/I27</f>
         <v>1.4230769230769231</v>
       </c>
@@ -2142,17 +2146,17 @@
         <f>K27-L27</f>
         <v>-2143</v>
       </c>
-      <c r="N27" s="18">
+      <c r="N27" s="17">
         <f>K27/F27</f>
         <v>519.07692307692309</v>
       </c>
-      <c r="O27" s="15">
+      <c r="O27" s="14">
         <v>0.38500000000000001</v>
       </c>
-      <c r="P27" s="15">
+      <c r="P27" s="14">
         <v>0.2</v>
       </c>
-      <c r="Q27" s="16">
+      <c r="Q27" s="19">
         <v>0.5</v>
       </c>
       <c r="R27" s="11"/>
@@ -2168,13 +2172,13 @@
       <c r="AB27" s="11"/>
     </row>
     <row r="28" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="12"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
+      <c r="A28" s="18"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="18"/>
       <c r="D28" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="E28" s="17" t="s">
+      <c r="E28" s="16" t="s">
         <v>28</v>
       </c>
       <c r="F28" s="11" t="s">
@@ -2189,7 +2193,7 @@
       <c r="I28" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="J28" s="13" t="s">
+      <c r="J28" s="12" t="s">
         <v>28</v>
       </c>
       <c r="K28" s="11" t="s">
@@ -2201,16 +2205,16 @@
       <c r="M28" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="N28" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="O28" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="P28" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q28" s="16" t="s">
+      <c r="N28" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="O28" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="P28" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q28" s="19" t="s">
         <v>28</v>
       </c>
       <c r="R28" s="11"/>
@@ -2226,11 +2230,11 @@
       <c r="AB28" s="11"/>
     </row>
     <row r="29" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="12" t="s">
+      <c r="A29" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="18"/>
       <c r="D29" s="11" t="s">
         <v>0</v>
       </c>
@@ -2286,15 +2290,15 @@
       <c r="AB29" s="11"/>
     </row>
     <row r="30" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="12" t="s">
+      <c r="A30" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="18"/>
       <c r="D30" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="E30" s="17">
+      <c r="E30" s="16">
         <v>8</v>
       </c>
       <c r="F30" s="11">
@@ -2309,7 +2313,7 @@
       <c r="I30" s="11">
         <v>36</v>
       </c>
-      <c r="J30" s="13">
+      <c r="J30" s="12">
         <f>(G30+H30)/I30</f>
         <v>1.8611111111111112</v>
       </c>
@@ -2322,17 +2326,17 @@
       <c r="M30" s="11">
         <v>-15</v>
       </c>
-      <c r="N30" s="18">
+      <c r="N30" s="17">
         <f>K30/F30</f>
         <v>541.64705882352939</v>
       </c>
-      <c r="O30" s="15">
+      <c r="O30" s="14">
         <v>0.64700000000000002</v>
       </c>
-      <c r="P30" s="15">
+      <c r="P30" s="14">
         <v>0.54500000000000004</v>
       </c>
-      <c r="Q30" s="16">
+      <c r="Q30" s="19">
         <v>8.3000000000000004E-2</v>
       </c>
       <c r="R30" s="11"/>
@@ -2348,13 +2352,13 @@
       <c r="AB30" s="11"/>
     </row>
     <row r="31" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="12"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
+      <c r="A31" s="18"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="18"/>
       <c r="D31" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="17">
+      <c r="E31" s="16">
         <v>30</v>
       </c>
       <c r="F31" s="11">
@@ -2369,7 +2373,7 @@
       <c r="I31" s="11">
         <v>28</v>
       </c>
-      <c r="J31" s="13">
+      <c r="J31" s="12">
         <f>(G31+H31)/I31</f>
         <v>1.5357142857142858</v>
       </c>
@@ -2382,17 +2386,17 @@
       <c r="M31" s="11">
         <v>-1011</v>
       </c>
-      <c r="N31" s="18">
+      <c r="N31" s="17">
         <f>K31/F31</f>
         <v>314.63333333333333</v>
       </c>
-      <c r="O31" s="15">
+      <c r="O31" s="14">
         <v>0.26740000000000003</v>
       </c>
-      <c r="P31" s="15">
+      <c r="P31" s="14">
         <v>0.125</v>
       </c>
-      <c r="Q31" s="16">
+      <c r="Q31" s="19">
         <v>1</v>
       </c>
       <c r="R31" s="11"/>
@@ -2408,13 +2412,13 @@
       <c r="AB31" s="11"/>
     </row>
     <row r="32" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="12"/>
-      <c r="B32" s="12"/>
-      <c r="C32" s="12"/>
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
       <c r="D32" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E32" s="17">
+      <c r="E32" s="16">
         <v>13</v>
       </c>
       <c r="F32" s="11">
@@ -2429,7 +2433,7 @@
       <c r="I32" s="11">
         <v>39</v>
       </c>
-      <c r="J32" s="13">
+      <c r="J32" s="12">
         <f>(G32+H32)/I32</f>
         <v>1.8717948717948718</v>
       </c>
@@ -2442,17 +2446,17 @@
       <c r="M32" s="11">
         <v>759</v>
       </c>
-      <c r="N32" s="18">
+      <c r="N32" s="17">
         <f>K32/F32</f>
         <v>429.125</v>
       </c>
-      <c r="O32" s="15">
+      <c r="O32" s="14">
         <v>0.52500000000000002</v>
       </c>
-      <c r="P32" s="15">
+      <c r="P32" s="14">
         <v>0.42899999999999999</v>
       </c>
-      <c r="Q32" s="16">
+      <c r="Q32" s="19">
         <v>0.111</v>
       </c>
       <c r="R32" s="11"/>
@@ -2468,13 +2472,13 @@
       <c r="AB32" s="11"/>
     </row>
     <row r="33" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="12"/>
-      <c r="B33" s="12"/>
-      <c r="C33" s="12"/>
+      <c r="A33" s="18"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="18"/>
       <c r="D33" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="E33" s="17">
+      <c r="E33" s="16">
         <v>35</v>
       </c>
       <c r="F33" s="11">
@@ -2489,7 +2493,7 @@
       <c r="I33" s="11">
         <v>24</v>
       </c>
-      <c r="J33" s="13">
+      <c r="J33" s="12">
         <f>(G33+H33)/I33</f>
         <v>1.125</v>
       </c>
@@ -2500,20 +2504,20 @@
         <v>10028</v>
       </c>
       <c r="M33" s="11">
-        <f t="shared" ref="M33:M35" si="4">K33-L33</f>
+        <f t="shared" ref="M33" si="4">K33-L33</f>
         <v>-2631</v>
       </c>
-      <c r="N33" s="18">
+      <c r="N33" s="17">
         <f>K33/F33</f>
         <v>308.20833333333331</v>
       </c>
-      <c r="O33" s="15">
+      <c r="O33" s="14">
         <v>0.20799999999999999</v>
       </c>
-      <c r="P33" s="15">
+      <c r="P33" s="14">
         <v>0</v>
       </c>
-      <c r="Q33" s="16">
+      <c r="Q33" s="19">
         <v>0</v>
       </c>
       <c r="R33" s="11"/>
@@ -2529,13 +2533,13 @@
       <c r="AB33" s="11"/>
     </row>
     <row r="34" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="12"/>
-      <c r="B34" s="12"/>
-      <c r="C34" s="12"/>
+      <c r="A34" s="18"/>
+      <c r="B34" s="18"/>
+      <c r="C34" s="18"/>
       <c r="D34" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="E34" s="17">
+      <c r="E34" s="16">
         <v>22</v>
       </c>
       <c r="F34" s="11">
@@ -2550,7 +2554,7 @@
       <c r="I34" s="11">
         <v>31</v>
       </c>
-      <c r="J34" s="13">
+      <c r="J34" s="12">
         <f>(G34+H34)/I34</f>
         <v>2.193548387096774</v>
       </c>
@@ -2564,17 +2568,17 @@
         <f>K34-L34</f>
         <v>-779</v>
       </c>
-      <c r="N34" s="18">
+      <c r="N34" s="17">
         <f>K34/F34</f>
         <v>408.9</v>
       </c>
-      <c r="O34" s="15">
+      <c r="O34" s="14">
         <v>0.46700000000000003</v>
       </c>
-      <c r="P34" s="15">
+      <c r="P34" s="14">
         <v>0.42899999999999999</v>
       </c>
-      <c r="Q34" s="16">
+      <c r="Q34" s="19">
         <v>0.16700000000000001</v>
       </c>
       <c r="R34" s="11"/>
@@ -2590,13 +2594,13 @@
       <c r="AB34" s="11"/>
     </row>
     <row r="35" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="12"/>
-      <c r="B35" s="12"/>
-      <c r="C35" s="12"/>
+      <c r="A35" s="18"/>
+      <c r="B35" s="18"/>
+      <c r="C35" s="18"/>
       <c r="D35" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="E35" s="17" t="s">
+      <c r="E35" s="16" t="s">
         <v>28</v>
       </c>
       <c r="F35" s="11" t="s">
@@ -2611,7 +2615,7 @@
       <c r="I35" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="J35" s="13" t="s">
+      <c r="J35" s="12" t="s">
         <v>28</v>
       </c>
       <c r="K35" s="11" t="s">
@@ -2623,16 +2627,16 @@
       <c r="M35" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="N35" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="O35" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="P35" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q35" s="16" t="s">
+      <c r="N35" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="O35" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="P35" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q35" s="19" t="s">
         <v>28</v>
       </c>
       <c r="R35" s="11"/>
@@ -2648,11 +2652,11 @@
       <c r="AB35" s="11"/>
     </row>
     <row r="36" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="12" t="s">
+      <c r="A36" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B36" s="12"/>
-      <c r="C36" s="12"/>
+      <c r="B36" s="18"/>
+      <c r="C36" s="18"/>
       <c r="D36" s="11" t="s">
         <v>0</v>
       </c>
@@ -2708,51 +2712,51 @@
       <c r="AB36" s="11"/>
     </row>
     <row r="37" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="12" t="s">
+      <c r="A37" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="B37" s="12"/>
-      <c r="C37" s="12"/>
+      <c r="B37" s="18"/>
+      <c r="C37" s="18"/>
       <c r="D37" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="E37" s="17" t="s">
+      <c r="E37" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="F37" s="17" t="s">
+      <c r="F37" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="G37" s="17" t="s">
+      <c r="G37" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="H37" s="17" t="s">
+      <c r="H37" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="I37" s="17" t="s">
+      <c r="I37" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="J37" s="17" t="s">
+      <c r="J37" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="K37" s="17" t="s">
+      <c r="K37" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="L37" s="17" t="s">
+      <c r="L37" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="M37" s="17" t="s">
+      <c r="M37" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="N37" s="18" t="s">
+      <c r="N37" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="O37" s="17" t="s">
+      <c r="O37" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="P37" s="17" t="s">
+      <c r="P37" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="Q37" s="17" t="s">
+      <c r="Q37" s="19" t="s">
         <v>29</v>
       </c>
       <c r="R37" s="11"/>
@@ -2768,13 +2772,13 @@
       <c r="AB37" s="11"/>
     </row>
     <row r="38" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="12"/>
-      <c r="B38" s="12"/>
-      <c r="C38" s="12"/>
+      <c r="A38" s="18"/>
+      <c r="B38" s="18"/>
+      <c r="C38" s="18"/>
       <c r="D38" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E38" s="17" t="s">
+      <c r="E38" s="16" t="s">
         <v>28</v>
       </c>
       <c r="F38" s="11" t="s">
@@ -2789,7 +2793,7 @@
       <c r="I38" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="J38" s="13" t="s">
+      <c r="J38" s="12" t="s">
         <v>28</v>
       </c>
       <c r="K38" s="11" t="s">
@@ -2801,16 +2805,16 @@
       <c r="M38" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="N38" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="O38" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="P38" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q38" s="16" t="s">
+      <c r="N38" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="O38" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="P38" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q38" s="19" t="s">
         <v>28</v>
       </c>
       <c r="R38" s="11"/>
@@ -2826,13 +2830,13 @@
       <c r="AB38" s="11"/>
     </row>
     <row r="39" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="12"/>
-      <c r="B39" s="12"/>
-      <c r="C39" s="12"/>
+      <c r="A39" s="18"/>
+      <c r="B39" s="18"/>
+      <c r="C39" s="18"/>
       <c r="D39" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E39" s="17" t="s">
+      <c r="E39" s="16" t="s">
         <v>28</v>
       </c>
       <c r="F39" s="11" t="s">
@@ -2847,7 +2851,7 @@
       <c r="I39" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="J39" s="13" t="s">
+      <c r="J39" s="12" t="s">
         <v>28</v>
       </c>
       <c r="K39" s="11" t="s">
@@ -2859,16 +2863,16 @@
       <c r="M39" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="N39" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="O39" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="P39" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q39" s="16" t="s">
+      <c r="N39" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="O39" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="P39" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q39" s="19" t="s">
         <v>28</v>
       </c>
       <c r="R39" s="11"/>
@@ -2884,13 +2888,13 @@
       <c r="AB39" s="11"/>
     </row>
     <row r="40" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="12"/>
-      <c r="B40" s="12"/>
-      <c r="C40" s="12"/>
+      <c r="A40" s="18"/>
+      <c r="B40" s="18"/>
+      <c r="C40" s="18"/>
       <c r="D40" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="E40" s="17" t="s">
+      <c r="E40" s="16" t="s">
         <v>28</v>
       </c>
       <c r="F40" s="11" t="s">
@@ -2905,7 +2909,7 @@
       <c r="I40" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="J40" s="13" t="s">
+      <c r="J40" s="12" t="s">
         <v>28</v>
       </c>
       <c r="K40" s="11" t="s">
@@ -2917,16 +2921,16 @@
       <c r="M40" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="N40" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="O40" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="P40" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q40" s="16" t="s">
+      <c r="N40" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="O40" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="P40" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q40" s="19" t="s">
         <v>28</v>
       </c>
       <c r="R40" s="11"/>
@@ -2942,13 +2946,13 @@
       <c r="AB40" s="11"/>
     </row>
     <row r="41" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="12"/>
-      <c r="B41" s="12"/>
-      <c r="C41" s="12"/>
+      <c r="A41" s="18"/>
+      <c r="B41" s="18"/>
+      <c r="C41" s="18"/>
       <c r="D41" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="E41" s="17" t="s">
+      <c r="E41" s="16" t="s">
         <v>28</v>
       </c>
       <c r="F41" s="11" t="s">
@@ -2963,7 +2967,7 @@
       <c r="I41" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="J41" s="13" t="s">
+      <c r="J41" s="12" t="s">
         <v>28</v>
       </c>
       <c r="K41" s="11" t="s">
@@ -2975,16 +2979,16 @@
       <c r="M41" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="N41" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="O41" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="P41" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q41" s="16" t="s">
+      <c r="N41" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="O41" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="P41" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q41" s="19" t="s">
         <v>28</v>
       </c>
       <c r="R41" s="11"/>
@@ -3000,13 +3004,13 @@
       <c r="AB41" s="11"/>
     </row>
     <row r="42" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="12"/>
-      <c r="B42" s="12"/>
-      <c r="C42" s="12"/>
+      <c r="A42" s="18"/>
+      <c r="B42" s="18"/>
+      <c r="C42" s="18"/>
       <c r="D42" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="E42" s="17">
+      <c r="E42" s="16">
         <v>15</v>
       </c>
       <c r="F42" s="11">
@@ -3021,7 +3025,7 @@
       <c r="I42" s="11">
         <v>22</v>
       </c>
-      <c r="J42" s="13">
+      <c r="J42" s="12">
         <f>(G42+H42)/I42</f>
         <v>2.1363636363636362</v>
       </c>
@@ -3032,20 +3036,20 @@
         <v>8989</v>
       </c>
       <c r="M42" s="11">
-        <f t="shared" ref="M40:M42" si="5">K42-L42</f>
+        <f t="shared" ref="M42" si="5">K42-L42</f>
         <v>834</v>
       </c>
-      <c r="N42" s="18">
+      <c r="N42" s="17">
         <f>K42/F42</f>
         <v>427.08695652173913</v>
       </c>
-      <c r="O42" s="15">
+      <c r="O42" s="14">
         <v>0.435</v>
       </c>
-      <c r="P42" s="15">
+      <c r="P42" s="14">
         <v>0.4</v>
       </c>
-      <c r="Q42" s="16">
+      <c r="Q42" s="19">
         <v>0.25</v>
       </c>
       <c r="R42" s="11"/>
@@ -3061,11 +3065,11 @@
       <c r="AB42" s="11"/>
     </row>
     <row r="43" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="12" t="s">
+      <c r="A43" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B43" s="12"/>
-      <c r="C43" s="12"/>
+      <c r="B43" s="18"/>
+      <c r="C43" s="18"/>
       <c r="D43" s="11" t="s">
         <v>0</v>
       </c>
@@ -3096,7 +3100,7 @@
       <c r="M43" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="N43" s="18" t="s">
+      <c r="N43" s="17" t="s">
         <v>14</v>
       </c>
       <c r="O43" s="11" t="s">
@@ -3121,15 +3125,15 @@
       <c r="AB43" s="11"/>
     </row>
     <row r="44" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="12" t="s">
+      <c r="A44" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="B44" s="12"/>
-      <c r="C44" s="12"/>
+      <c r="B44" s="18"/>
+      <c r="C44" s="18"/>
       <c r="D44" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="E44" s="17" t="s">
+      <c r="E44" s="16" t="s">
         <v>28</v>
       </c>
       <c r="F44" s="11" t="s">
@@ -3144,7 +3148,7 @@
       <c r="I44" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="J44" s="13" t="s">
+      <c r="J44" s="12" t="s">
         <v>28</v>
       </c>
       <c r="K44" s="11" t="s">
@@ -3156,17 +3160,17 @@
       <c r="M44" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="N44" s="18" t="s">
+      <c r="N44" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="O44" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="P44" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q44" s="16" t="s">
-        <v>28</v>
+      <c r="O44" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="P44" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q44" s="19" t="s">
+        <v>29</v>
       </c>
       <c r="R44" s="11"/>
       <c r="S44" s="11"/>
@@ -3181,13 +3185,13 @@
       <c r="AB44" s="11"/>
     </row>
     <row r="45" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="12"/>
-      <c r="B45" s="12"/>
-      <c r="C45" s="12"/>
+      <c r="A45" s="18"/>
+      <c r="B45" s="18"/>
+      <c r="C45" s="18"/>
       <c r="D45" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E45" s="17" t="s">
+      <c r="E45" s="16" t="s">
         <v>28</v>
       </c>
       <c r="F45" s="11" t="s">
@@ -3202,7 +3206,7 @@
       <c r="I45" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="J45" s="13" t="s">
+      <c r="J45" s="12" t="s">
         <v>28</v>
       </c>
       <c r="K45" s="11" t="s">
@@ -3214,16 +3218,16 @@
       <c r="M45" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="N45" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="O45" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="P45" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q45" s="16" t="s">
+      <c r="N45" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="O45" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="P45" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q45" s="19" t="s">
         <v>28</v>
       </c>
       <c r="R45" s="11"/>
@@ -3239,13 +3243,13 @@
       <c r="AB45" s="11"/>
     </row>
     <row r="46" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="12"/>
-      <c r="B46" s="12"/>
-      <c r="C46" s="12"/>
+      <c r="A46" s="18"/>
+      <c r="B46" s="18"/>
+      <c r="C46" s="18"/>
       <c r="D46" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E46" s="17" t="s">
+      <c r="E46" s="16" t="s">
         <v>28</v>
       </c>
       <c r="F46" s="11" t="s">
@@ -3260,7 +3264,7 @@
       <c r="I46" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="J46" s="13" t="s">
+      <c r="J46" s="12" t="s">
         <v>28</v>
       </c>
       <c r="K46" s="11" t="s">
@@ -3272,16 +3276,16 @@
       <c r="M46" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="N46" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="O46" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="P46" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q46" s="16" t="s">
+      <c r="N46" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="O46" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="P46" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q46" s="19" t="s">
         <v>28</v>
       </c>
       <c r="R46" s="11"/>
@@ -3297,13 +3301,13 @@
       <c r="AB46" s="11"/>
     </row>
     <row r="47" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="12"/>
-      <c r="B47" s="12"/>
-      <c r="C47" s="12"/>
+      <c r="A47" s="18"/>
+      <c r="B47" s="18"/>
+      <c r="C47" s="18"/>
       <c r="D47" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="E47" s="17" t="s">
+      <c r="E47" s="16" t="s">
         <v>28</v>
       </c>
       <c r="F47" s="11" t="s">
@@ -3318,7 +3322,7 @@
       <c r="I47" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="J47" s="13" t="s">
+      <c r="J47" s="12" t="s">
         <v>28</v>
       </c>
       <c r="K47" s="11" t="s">
@@ -3330,16 +3334,16 @@
       <c r="M47" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="N47" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="O47" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="P47" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q47" s="16" t="s">
+      <c r="N47" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="O47" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="P47" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q47" s="19" t="s">
         <v>28</v>
       </c>
       <c r="R47" s="11"/>
@@ -3355,13 +3359,13 @@
       <c r="AB47" s="11"/>
     </row>
     <row r="48" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="12"/>
-      <c r="B48" s="12"/>
-      <c r="C48" s="12"/>
+      <c r="A48" s="18"/>
+      <c r="B48" s="18"/>
+      <c r="C48" s="18"/>
       <c r="D48" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="E48" s="17" t="s">
+      <c r="E48" s="16" t="s">
         <v>28</v>
       </c>
       <c r="F48" s="11" t="s">
@@ -3376,7 +3380,7 @@
       <c r="I48" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="J48" s="13" t="s">
+      <c r="J48" s="12" t="s">
         <v>28</v>
       </c>
       <c r="K48" s="11" t="s">
@@ -3388,16 +3392,16 @@
       <c r="M48" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="N48" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="O48" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="P48" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q48" s="16" t="s">
+      <c r="N48" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="O48" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="P48" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q48" s="19" t="s">
         <v>28</v>
       </c>
       <c r="R48" s="11"/>
@@ -3413,13 +3417,13 @@
       <c r="AB48" s="11"/>
     </row>
     <row r="49" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="12"/>
-      <c r="B49" s="12"/>
-      <c r="C49" s="12"/>
+      <c r="A49" s="18"/>
+      <c r="B49" s="18"/>
+      <c r="C49" s="18"/>
       <c r="D49" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="E49" s="17">
+      <c r="E49" s="16">
         <v>37</v>
       </c>
       <c r="F49" s="11">
@@ -3434,8 +3438,8 @@
       <c r="I49" s="11">
         <v>25</v>
       </c>
-      <c r="J49" s="13">
-        <f t="shared" ref="J47:J49" si="6">(G49+H49)/I49</f>
+      <c r="J49" s="12">
+        <f t="shared" ref="J49" si="6">(G49+H49)/I49</f>
         <v>1.1200000000000001</v>
       </c>
       <c r="K49" s="11">
@@ -3445,20 +3449,20 @@
         <v>10306</v>
       </c>
       <c r="M49" s="11">
-        <f t="shared" ref="M47:M49" si="7">K49-L49</f>
+        <f t="shared" ref="M49" si="7">K49-L49</f>
         <v>-2193</v>
       </c>
-      <c r="N49" s="18">
+      <c r="N49" s="17">
         <f>K49/F49</f>
         <v>338.04166666666669</v>
       </c>
-      <c r="O49" s="15">
+      <c r="O49" s="14">
         <v>0.41699999999999998</v>
       </c>
-      <c r="P49" s="15">
+      <c r="P49" s="14">
         <v>0.1</v>
       </c>
-      <c r="Q49" s="16">
+      <c r="Q49" s="19">
         <v>0</v>
       </c>
       <c r="R49" s="11"/>
@@ -3474,11 +3478,11 @@
       <c r="AB49" s="11"/>
     </row>
     <row r="50" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="12" t="s">
+      <c r="A50" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B50" s="12"/>
-      <c r="C50" s="12"/>
+      <c r="B50" s="18"/>
+      <c r="C50" s="18"/>
       <c r="D50" s="11" t="s">
         <v>0</v>
       </c>
@@ -3534,15 +3538,15 @@
       <c r="AB50" s="11"/>
     </row>
     <row r="51" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="12" t="s">
+      <c r="A51" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="B51" s="12"/>
-      <c r="C51" s="12"/>
+      <c r="B51" s="18"/>
+      <c r="C51" s="18"/>
       <c r="D51" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="E51" s="17" t="s">
+      <c r="E51" s="16" t="s">
         <v>28</v>
       </c>
       <c r="F51" s="11" t="s">
@@ -3557,7 +3561,7 @@
       <c r="I51" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="J51" s="13" t="s">
+      <c r="J51" s="12" t="s">
         <v>28</v>
       </c>
       <c r="K51" s="11" t="s">
@@ -3569,17 +3573,17 @@
       <c r="M51" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="N51" s="18" t="s">
+      <c r="N51" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="O51" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="P51" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q51" s="16" t="s">
-        <v>28</v>
+      <c r="O51" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="P51" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q51" s="19" t="s">
+        <v>29</v>
       </c>
       <c r="R51" s="11"/>
       <c r="S51" s="11"/>
@@ -3594,13 +3598,13 @@
       <c r="AB51" s="11"/>
     </row>
     <row r="52" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="12"/>
-      <c r="B52" s="12"/>
-      <c r="C52" s="12"/>
+      <c r="A52" s="18"/>
+      <c r="B52" s="18"/>
+      <c r="C52" s="18"/>
       <c r="D52" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E52" s="17" t="s">
+      <c r="E52" s="16" t="s">
         <v>28</v>
       </c>
       <c r="F52" s="11" t="s">
@@ -3615,7 +3619,7 @@
       <c r="I52" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="J52" s="13" t="s">
+      <c r="J52" s="12" t="s">
         <v>28</v>
       </c>
       <c r="K52" s="11" t="s">
@@ -3627,16 +3631,16 @@
       <c r="M52" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="N52" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="O52" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="P52" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q52" s="16" t="s">
+      <c r="N52" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="O52" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="P52" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q52" s="19" t="s">
         <v>28</v>
       </c>
       <c r="R52" s="11"/>
@@ -3652,13 +3656,13 @@
       <c r="AB52" s="11"/>
     </row>
     <row r="53" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="12"/>
-      <c r="B53" s="12"/>
-      <c r="C53" s="12"/>
+      <c r="A53" s="18"/>
+      <c r="B53" s="18"/>
+      <c r="C53" s="18"/>
       <c r="D53" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E53" s="17">
+      <c r="E53" s="16">
         <v>7</v>
       </c>
       <c r="F53" s="11">
@@ -3673,7 +3677,7 @@
       <c r="I53" s="11">
         <v>29</v>
       </c>
-      <c r="J53" s="13">
+      <c r="J53" s="12">
         <f t="shared" ref="J53" si="8">(G53+H53)/I53</f>
         <v>3.3793103448275863</v>
       </c>
@@ -3686,17 +3690,17 @@
       <c r="M53" s="11">
         <v>3361</v>
       </c>
-      <c r="N53" s="18">
+      <c r="N53" s="17">
         <f>K53/F53</f>
         <v>634.14705882352939</v>
       </c>
-      <c r="O53" s="15">
+      <c r="O53" s="14">
         <v>0.61799999999999999</v>
       </c>
-      <c r="P53" s="15">
+      <c r="P53" s="14">
         <v>0.57099999999999995</v>
       </c>
-      <c r="Q53" s="16">
+      <c r="Q53" s="19">
         <v>0.41699999999999998</v>
       </c>
       <c r="R53" s="11"/>
@@ -3712,13 +3716,13 @@
       <c r="AB53" s="11"/>
     </row>
     <row r="54" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="12"/>
-      <c r="B54" s="12"/>
-      <c r="C54" s="12"/>
+      <c r="A54" s="18"/>
+      <c r="B54" s="18"/>
+      <c r="C54" s="18"/>
       <c r="D54" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="E54" s="17" t="s">
+      <c r="E54" s="16" t="s">
         <v>28</v>
       </c>
       <c r="F54" s="11" t="s">
@@ -3733,7 +3737,7 @@
       <c r="I54" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="J54" s="13" t="s">
+      <c r="J54" s="12" t="s">
         <v>28</v>
       </c>
       <c r="K54" s="11" t="s">
@@ -3745,16 +3749,16 @@
       <c r="M54" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="N54" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="O54" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="P54" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q54" s="16" t="s">
+      <c r="N54" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="O54" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="P54" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q54" s="19" t="s">
         <v>28</v>
       </c>
       <c r="R54" s="11"/>
@@ -3770,13 +3774,13 @@
       <c r="AB54" s="11"/>
     </row>
     <row r="55" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="12"/>
-      <c r="B55" s="12"/>
-      <c r="C55" s="12"/>
+      <c r="A55" s="18"/>
+      <c r="B55" s="18"/>
+      <c r="C55" s="18"/>
       <c r="D55" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="E55" s="17" t="s">
+      <c r="E55" s="16" t="s">
         <v>28</v>
       </c>
       <c r="F55" s="11" t="s">
@@ -3791,7 +3795,7 @@
       <c r="I55" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="J55" s="13" t="s">
+      <c r="J55" s="12" t="s">
         <v>28</v>
       </c>
       <c r="K55" s="11" t="s">
@@ -3803,16 +3807,16 @@
       <c r="M55" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="N55" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="O55" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="P55" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q55" s="16" t="s">
+      <c r="N55" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="O55" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="P55" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q55" s="19" t="s">
         <v>28</v>
       </c>
       <c r="R55" s="11"/>
@@ -3828,13 +3832,13 @@
       <c r="AB55" s="11"/>
     </row>
     <row r="56" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="12"/>
-      <c r="B56" s="12"/>
-      <c r="C56" s="12"/>
+      <c r="A56" s="18"/>
+      <c r="B56" s="18"/>
+      <c r="C56" s="18"/>
       <c r="D56" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="E56" s="17">
+      <c r="E56" s="16">
         <v>18</v>
       </c>
       <c r="F56" s="11">
@@ -3849,7 +3853,7 @@
       <c r="I56" s="11">
         <v>43</v>
       </c>
-      <c r="J56" s="13">
+      <c r="J56" s="12">
         <f t="shared" ref="J56" si="9">(G56+H56)/I56</f>
         <v>1.5116279069767442</v>
       </c>
@@ -3863,17 +3867,17 @@
         <f t="shared" ref="M56" si="10">K56-L56</f>
         <v>-3174</v>
       </c>
-      <c r="N56" s="18">
+      <c r="N56" s="17">
         <f>K56/F56</f>
         <v>312.8095238095238</v>
       </c>
-      <c r="O56" s="15">
+      <c r="O56" s="14">
         <v>0.45200000000000001</v>
       </c>
-      <c r="P56" s="15">
+      <c r="P56" s="14">
         <v>0.26300000000000001</v>
       </c>
-      <c r="Q56" s="16">
+      <c r="Q56" s="19">
         <v>0</v>
       </c>
       <c r="R56" s="11"/>
@@ -3889,11 +3893,11 @@
       <c r="AB56" s="11"/>
     </row>
     <row r="57" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="12" t="s">
+      <c r="A57" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B57" s="12"/>
-      <c r="C57" s="12"/>
+      <c r="B57" s="18"/>
+      <c r="C57" s="18"/>
       <c r="D57" s="11" t="s">
         <v>0</v>
       </c>
@@ -3949,15 +3953,15 @@
       <c r="AB57" s="11"/>
     </row>
     <row r="58" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="12" t="s">
+      <c r="A58" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="B58" s="12"/>
-      <c r="C58" s="12"/>
+      <c r="B58" s="18"/>
+      <c r="C58" s="18"/>
       <c r="D58" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="E58" s="17" t="s">
+      <c r="E58" s="16" t="s">
         <v>28</v>
       </c>
       <c r="F58" s="11" t="s">
@@ -3972,7 +3976,7 @@
       <c r="I58" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="J58" s="13" t="s">
+      <c r="J58" s="12" t="s">
         <v>28</v>
       </c>
       <c r="K58" s="11" t="s">
@@ -3984,17 +3988,17 @@
       <c r="M58" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="N58" s="18" t="s">
+      <c r="N58" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="O58" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="P58" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q58" s="16" t="s">
-        <v>28</v>
+      <c r="O58" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="P58" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q58" s="19" t="s">
+        <v>29</v>
       </c>
       <c r="R58" s="11"/>
       <c r="S58" s="11"/>
@@ -4009,13 +4013,13 @@
       <c r="AB58" s="11"/>
     </row>
     <row r="59" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="12"/>
-      <c r="B59" s="12"/>
-      <c r="C59" s="12"/>
+      <c r="A59" s="18"/>
+      <c r="B59" s="18"/>
+      <c r="C59" s="18"/>
       <c r="D59" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E59" s="17" t="s">
+      <c r="E59" s="16" t="s">
         <v>28</v>
       </c>
       <c r="F59" s="11" t="s">
@@ -4030,7 +4034,7 @@
       <c r="I59" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="J59" s="13" t="s">
+      <c r="J59" s="12" t="s">
         <v>28</v>
       </c>
       <c r="K59" s="11" t="s">
@@ -4042,16 +4046,16 @@
       <c r="M59" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="N59" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="O59" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="P59" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q59" s="16" t="s">
+      <c r="N59" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="O59" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="P59" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q59" s="19" t="s">
         <v>28</v>
       </c>
       <c r="R59" s="11"/>
@@ -4067,13 +4071,13 @@
       <c r="AB59" s="11"/>
     </row>
     <row r="60" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="12"/>
-      <c r="B60" s="12"/>
-      <c r="C60" s="12"/>
+      <c r="A60" s="18"/>
+      <c r="B60" s="18"/>
+      <c r="C60" s="18"/>
       <c r="D60" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E60" s="17">
+      <c r="E60" s="16">
         <v>25</v>
       </c>
       <c r="F60" s="11">
@@ -4088,7 +4092,7 @@
       <c r="I60" s="11">
         <v>30</v>
       </c>
-      <c r="J60" s="13">
+      <c r="J60" s="12">
         <f t="shared" ref="J60" si="11">(G60+H60)/I60</f>
         <v>1.9666666666666666</v>
       </c>
@@ -4101,17 +4105,17 @@
       <c r="M60" s="11">
         <v>-2554</v>
       </c>
-      <c r="N60" s="18">
+      <c r="N60" s="17">
         <f>K60/F60</f>
         <v>456.46666666666664</v>
       </c>
-      <c r="O60" s="15">
+      <c r="O60" s="14">
         <v>0.433</v>
       </c>
-      <c r="P60" s="15">
+      <c r="P60" s="14">
         <v>0.308</v>
       </c>
-      <c r="Q60" s="16">
+      <c r="Q60" s="19">
         <v>0.25</v>
       </c>
       <c r="R60" s="11"/>
@@ -4127,13 +4131,13 @@
       <c r="AB60" s="11"/>
     </row>
     <row r="61" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="12"/>
-      <c r="B61" s="12"/>
-      <c r="C61" s="12"/>
+      <c r="A61" s="18"/>
+      <c r="B61" s="18"/>
+      <c r="C61" s="18"/>
       <c r="D61" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="E61" s="17" t="s">
+      <c r="E61" s="16" t="s">
         <v>28</v>
       </c>
       <c r="F61" s="11" t="s">
@@ -4148,7 +4152,7 @@
       <c r="I61" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="J61" s="13" t="s">
+      <c r="J61" s="12" t="s">
         <v>28</v>
       </c>
       <c r="K61" s="11" t="s">
@@ -4160,16 +4164,16 @@
       <c r="M61" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="N61" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="O61" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="P61" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q61" s="16" t="s">
+      <c r="N61" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="O61" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="P61" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q61" s="19" t="s">
         <v>28</v>
       </c>
       <c r="R61" s="11"/>
@@ -4185,13 +4189,13 @@
       <c r="AB61" s="11"/>
     </row>
     <row r="62" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="12"/>
-      <c r="B62" s="12"/>
-      <c r="C62" s="12"/>
+      <c r="A62" s="18"/>
+      <c r="B62" s="18"/>
+      <c r="C62" s="18"/>
       <c r="D62" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="E62" s="17" t="s">
+      <c r="E62" s="16" t="s">
         <v>28</v>
       </c>
       <c r="F62" s="11" t="s">
@@ -4206,7 +4210,7 @@
       <c r="I62" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="J62" s="13" t="s">
+      <c r="J62" s="12" t="s">
         <v>28</v>
       </c>
       <c r="K62" s="11" t="s">
@@ -4218,16 +4222,16 @@
       <c r="M62" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="N62" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="O62" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="P62" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q62" s="16" t="s">
+      <c r="N62" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="O62" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="P62" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q62" s="19" t="s">
         <v>28</v>
       </c>
       <c r="R62" s="11"/>
@@ -4243,13 +4247,13 @@
       <c r="AB62" s="11"/>
     </row>
     <row r="63" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="12"/>
-      <c r="B63" s="12"/>
-      <c r="C63" s="12"/>
+      <c r="A63" s="18"/>
+      <c r="B63" s="18"/>
+      <c r="C63" s="18"/>
       <c r="D63" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="E63" s="17">
+      <c r="E63" s="16">
         <v>32</v>
       </c>
       <c r="F63" s="11">
@@ -4264,7 +4268,7 @@
       <c r="I63" s="11">
         <v>25</v>
       </c>
-      <c r="J63" s="13">
+      <c r="J63" s="12">
         <f t="shared" ref="J63" si="12">(G63+H63)/I63</f>
         <v>1.1599999999999999</v>
       </c>
@@ -4278,17 +4282,17 @@
         <f t="shared" ref="M63" si="13">K63-L63</f>
         <v>-3609</v>
       </c>
-      <c r="N63" s="18">
+      <c r="N63" s="17">
         <f>K63/F63</f>
         <v>312.375</v>
       </c>
-      <c r="O63" s="15">
+      <c r="O63" s="14">
         <v>0.625</v>
       </c>
-      <c r="P63" s="15">
+      <c r="P63" s="14">
         <v>0.4</v>
       </c>
-      <c r="Q63" s="16">
+      <c r="Q63" s="19">
         <v>0.16700000000000001</v>
       </c>
       <c r="R63" s="11"/>
@@ -4308,19 +4312,19 @@
       <c r="B64" s="11"/>
       <c r="C64" s="11"/>
       <c r="D64" s="11"/>
-      <c r="E64" s="17"/>
+      <c r="E64" s="16"/>
       <c r="F64" s="11"/>
       <c r="G64" s="11"/>
       <c r="H64" s="11"/>
       <c r="I64" s="11"/>
-      <c r="J64" s="13"/>
+      <c r="J64" s="12"/>
       <c r="K64" s="11"/>
       <c r="L64" s="11"/>
       <c r="M64" s="11"/>
-      <c r="N64" s="14"/>
-      <c r="O64" s="15"/>
-      <c r="P64" s="15"/>
-      <c r="Q64" s="16"/>
+      <c r="N64" s="13"/>
+      <c r="O64" s="14"/>
+      <c r="P64" s="14"/>
+      <c r="Q64" s="15"/>
       <c r="R64" s="11"/>
       <c r="S64" s="11"/>
       <c r="T64" s="11"/>
@@ -4338,19 +4342,19 @@
       <c r="B65" s="11"/>
       <c r="C65" s="11"/>
       <c r="D65" s="11"/>
-      <c r="E65" s="17"/>
+      <c r="E65" s="16"/>
       <c r="F65" s="11"/>
       <c r="G65" s="11"/>
       <c r="H65" s="11"/>
       <c r="I65" s="11"/>
-      <c r="J65" s="13"/>
+      <c r="J65" s="12"/>
       <c r="K65" s="11"/>
       <c r="L65" s="11"/>
       <c r="M65" s="11"/>
-      <c r="N65" s="14"/>
-      <c r="O65" s="15"/>
-      <c r="P65" s="15"/>
-      <c r="Q65" s="16"/>
+      <c r="N65" s="13"/>
+      <c r="O65" s="14"/>
+      <c r="P65" s="14"/>
+      <c r="Q65" s="15"/>
       <c r="R65" s="11"/>
       <c r="S65" s="11"/>
       <c r="T65" s="11"/>
@@ -4368,19 +4372,19 @@
       <c r="B66" s="11"/>
       <c r="C66" s="11"/>
       <c r="D66" s="11"/>
-      <c r="E66" s="17"/>
+      <c r="E66" s="16"/>
       <c r="F66" s="11"/>
       <c r="G66" s="11"/>
       <c r="H66" s="11"/>
       <c r="I66" s="11"/>
-      <c r="J66" s="13"/>
+      <c r="J66" s="12"/>
       <c r="K66" s="11"/>
       <c r="L66" s="11"/>
       <c r="M66" s="11"/>
-      <c r="N66" s="14"/>
-      <c r="O66" s="15"/>
-      <c r="P66" s="15"/>
-      <c r="Q66" s="16"/>
+      <c r="N66" s="13"/>
+      <c r="O66" s="14"/>
+      <c r="P66" s="14"/>
+      <c r="Q66" s="15"/>
       <c r="R66" s="11"/>
       <c r="S66" s="11"/>
       <c r="T66" s="11"/>
@@ -4398,19 +4402,19 @@
       <c r="B67" s="11"/>
       <c r="C67" s="11"/>
       <c r="D67" s="11"/>
-      <c r="E67" s="17"/>
+      <c r="E67" s="16"/>
       <c r="F67" s="11"/>
       <c r="G67" s="11"/>
       <c r="H67" s="11"/>
       <c r="I67" s="11"/>
-      <c r="J67" s="13"/>
+      <c r="J67" s="12"/>
       <c r="K67" s="11"/>
       <c r="L67" s="11"/>
       <c r="M67" s="11"/>
-      <c r="N67" s="14"/>
-      <c r="O67" s="15"/>
-      <c r="P67" s="15"/>
-      <c r="Q67" s="16"/>
+      <c r="N67" s="13"/>
+      <c r="O67" s="14"/>
+      <c r="P67" s="14"/>
+      <c r="Q67" s="15"/>
       <c r="R67" s="11"/>
       <c r="S67" s="11"/>
       <c r="T67" s="11"/>
@@ -4428,19 +4432,19 @@
       <c r="B68" s="11"/>
       <c r="C68" s="11"/>
       <c r="D68" s="11"/>
-      <c r="E68" s="17"/>
+      <c r="E68" s="16"/>
       <c r="F68" s="11"/>
       <c r="G68" s="11"/>
       <c r="H68" s="11"/>
       <c r="I68" s="11"/>
-      <c r="J68" s="13"/>
+      <c r="J68" s="12"/>
       <c r="K68" s="11"/>
       <c r="L68" s="11"/>
       <c r="M68" s="11"/>
-      <c r="N68" s="14"/>
-      <c r="O68" s="15"/>
-      <c r="P68" s="15"/>
-      <c r="Q68" s="16"/>
+      <c r="N68" s="13"/>
+      <c r="O68" s="14"/>
+      <c r="P68" s="14"/>
+      <c r="Q68" s="15"/>
       <c r="R68" s="11"/>
       <c r="S68" s="11"/>
       <c r="T68" s="11"/>
@@ -4458,19 +4462,19 @@
       <c r="B69" s="11"/>
       <c r="C69" s="11"/>
       <c r="D69" s="11"/>
-      <c r="E69" s="17"/>
+      <c r="E69" s="16"/>
       <c r="F69" s="11"/>
       <c r="G69" s="11"/>
       <c r="H69" s="11"/>
       <c r="I69" s="11"/>
-      <c r="J69" s="13"/>
+      <c r="J69" s="12"/>
       <c r="K69" s="11"/>
       <c r="L69" s="11"/>
       <c r="M69" s="11"/>
-      <c r="N69" s="14"/>
-      <c r="O69" s="15"/>
-      <c r="P69" s="15"/>
-      <c r="Q69" s="16"/>
+      <c r="N69" s="13"/>
+      <c r="O69" s="14"/>
+      <c r="P69" s="14"/>
+      <c r="Q69" s="15"/>
       <c r="R69" s="11"/>
       <c r="S69" s="11"/>
       <c r="T69" s="11"/>
@@ -4488,19 +4492,19 @@
       <c r="B70" s="11"/>
       <c r="C70" s="11"/>
       <c r="D70" s="11"/>
-      <c r="E70" s="17"/>
+      <c r="E70" s="16"/>
       <c r="F70" s="11"/>
       <c r="G70" s="11"/>
       <c r="H70" s="11"/>
       <c r="I70" s="11"/>
-      <c r="J70" s="13"/>
+      <c r="J70" s="12"/>
       <c r="K70" s="11"/>
       <c r="L70" s="11"/>
       <c r="M70" s="11"/>
-      <c r="N70" s="14"/>
-      <c r="O70" s="15"/>
-      <c r="P70" s="15"/>
-      <c r="Q70" s="16"/>
+      <c r="N70" s="13"/>
+      <c r="O70" s="14"/>
+      <c r="P70" s="14"/>
+      <c r="Q70" s="15"/>
       <c r="R70" s="11"/>
       <c r="S70" s="11"/>
       <c r="T70" s="11"/>
@@ -4605,6 +4609,17 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A23:C28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A30:C35"/>
+    <mergeCell ref="A2:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:C14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A16:C21"/>
     <mergeCell ref="A57:C57"/>
     <mergeCell ref="A58:C63"/>
     <mergeCell ref="A37:C42"/>
@@ -4612,17 +4627,6 @@
     <mergeCell ref="A44:C49"/>
     <mergeCell ref="A50:C50"/>
     <mergeCell ref="A51:C56"/>
-    <mergeCell ref="A2:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:C14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A16:C21"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A23:C28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A30:C35"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
